--- a/results/q3_output/表_调度前分析.xlsx
+++ b/results/q3_output/表_调度前分析.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
